--- a/Frontend/src/assets/templates/TablaCargaMasiva.xlsx
+++ b/Frontend/src/assets/templates/TablaCargaMasiva.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="233">
   <si>
     <t xml:space="preserve">codigo_producto</t>
   </si>
@@ -48,6 +48,21 @@
   </si>
   <si>
     <t xml:space="preserve">nombre_imagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">articulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sedronar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archivo_esp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">archivo_hds</t>
   </si>
   <si>
     <t xml:space="preserve">activo</t>
@@ -995,8 +1010,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:DO10"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
@@ -1004,12 +1019,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="114" min="15" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="119" min="20" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1052,19 +1070,19 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
@@ -1355,58 +1373,73 @@
       <c r="DJ1" s="2" t="s">
         <v>113</v>
       </c>
+      <c r="DK1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="DL1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="DM1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="DN1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="DO1" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>123</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3" t="s">
-        <v>122</v>
-      </c>
+      <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
+      <c r="S2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
@@ -1499,10 +1532,15 @@
       <c r="DH2" s="3"/>
       <c r="DI2" s="3"/>
       <c r="DJ2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="DK2" s="3"/>
+      <c r="DL2" s="3"/>
+      <c r="DM2" s="3"/>
+      <c r="DN2" s="3"/>
+      <c r="DO2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1513,28 +1551,28 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="4" t="s">
-        <v>128</v>
-      </c>
+      <c r="O3" s="4"/>
       <c r="P3" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="T3" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
@@ -1627,10 +1665,15 @@
       <c r="DH3" s="4"/>
       <c r="DI3" s="4"/>
       <c r="DJ3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="DK3" s="4"/>
+      <c r="DL3" s="4"/>
+      <c r="DM3" s="4"/>
+      <c r="DN3" s="4"/>
+      <c r="DO3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1641,28 +1684,28 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>131</v>
-      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="O4" s="4"/>
       <c r="P4" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+      <c r="T4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1755,10 +1798,15 @@
       <c r="DH4" s="4"/>
       <c r="DI4" s="4"/>
       <c r="DJ4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="DK4" s="4"/>
+      <c r="DL4" s="4"/>
+      <c r="DM4" s="4"/>
+      <c r="DN4" s="4"/>
+      <c r="DO4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1769,28 +1817,28 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="O5" s="4"/>
       <c r="P5" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+      <c r="T5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1883,8 +1931,13 @@
       <c r="DH5" s="4"/>
       <c r="DI5" s="4"/>
       <c r="DJ5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="DK5" s="4"/>
+      <c r="DL5" s="4"/>
+      <c r="DM5" s="4"/>
+      <c r="DN5" s="4"/>
+      <c r="DO5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1999,57 +2052,62 @@
       <c r="DH6" s="3"/>
       <c r="DI6" s="3"/>
       <c r="DJ6" s="3"/>
+      <c r="DK6" s="3"/>
+      <c r="DL6" s="3"/>
+      <c r="DM6" s="3"/>
+      <c r="DN6" s="3"/>
+      <c r="DO6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>123</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>122</v>
-      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
+      <c r="R7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
@@ -2143,10 +2201,15 @@
       <c r="DH7" s="3"/>
       <c r="DI7" s="3"/>
       <c r="DJ7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="DK7" s="3"/>
+      <c r="DL7" s="3"/>
+      <c r="DM7" s="3"/>
+      <c r="DN7" s="3"/>
+      <c r="DO7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2157,25 +2220,25 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="4" t="s">
-        <v>150</v>
-      </c>
+      <c r="O8" s="4"/>
       <c r="P8" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q8" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
+      <c r="T8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
@@ -2269,10 +2332,15 @@
       <c r="DH8" s="4"/>
       <c r="DI8" s="4"/>
       <c r="DJ8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="DK8" s="4"/>
+      <c r="DL8" s="4"/>
+      <c r="DM8" s="4"/>
+      <c r="DN8" s="4"/>
+      <c r="DO8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2283,25 +2351,25 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>151</v>
-      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="4" t="s">
-        <v>152</v>
-      </c>
+      <c r="O9" s="4"/>
       <c r="P9" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q9" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+      <c r="T9" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
@@ -2395,10 +2463,15 @@
       <c r="DH9" s="4"/>
       <c r="DI9" s="4"/>
       <c r="DJ9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="DK9" s="4"/>
+      <c r="DL9" s="4"/>
+      <c r="DM9" s="4"/>
+      <c r="DN9" s="4"/>
+      <c r="DO9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2409,25 +2482,25 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>154</v>
-      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4" t="s">
-        <v>155</v>
-      </c>
+      <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q10" s="4"/>
+        <v>127</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
+      <c r="T10" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
@@ -2521,6 +2594,11 @@
       <c r="DH10" s="4"/>
       <c r="DI10" s="4"/>
       <c r="DJ10" s="4"/>
+      <c r="DK10" s="4"/>
+      <c r="DL10" s="4"/>
+      <c r="DM10" s="4"/>
+      <c r="DN10" s="4"/>
+      <c r="DO10" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2560,7 +2638,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2568,82 +2646,82 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2651,37 +2729,37 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2689,27 +2767,27 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2717,27 +2795,27 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2745,7 +2823,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2753,17 +2831,17 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2771,17 +2849,17 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2789,17 +2867,17 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2807,17 +2885,17 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2825,17 +2903,17 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2843,17 +2921,17 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,17 +2939,17 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2879,12 +2957,12 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2892,67 +2970,67 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/Frontend/src/assets/templates/TablaCargaMasiva.xlsx
+++ b/Frontend/src/assets/templates/TablaCargaMasiva.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="228">
   <si>
     <t xml:space="preserve">codigo_producto</t>
   </si>
@@ -48,21 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve">nombre_imagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">articulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sedronar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archivo_esp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archivo_hds</t>
   </si>
   <si>
     <t xml:space="preserve">activo</t>
@@ -1010,8 +995,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DO10"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:DJ10"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
@@ -1019,15 +1004,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="119" min="20" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="114" min="15" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1070,19 +1052,19 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="2" t="s">
@@ -1373,73 +1355,58 @@
       <c r="DJ1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="DK1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="DL1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="DM1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="DN1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="DO1" s="2" t="s">
-        <v>118</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="O2" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q2" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="R2" s="3"/>
-      <c r="S2" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
@@ -1532,15 +1499,10 @@
       <c r="DH2" s="3"/>
       <c r="DI2" s="3"/>
       <c r="DJ2" s="3"/>
-      <c r="DK2" s="3"/>
-      <c r="DL2" s="3"/>
-      <c r="DM2" s="3"/>
-      <c r="DN2" s="3"/>
-      <c r="DO2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1551,28 +1513,28 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="P3" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
-      <c r="T3" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
@@ -1665,15 +1627,10 @@
       <c r="DH3" s="4"/>
       <c r="DI3" s="4"/>
       <c r="DJ3" s="4"/>
-      <c r="DK3" s="4"/>
-      <c r="DL3" s="4"/>
-      <c r="DM3" s="4"/>
-      <c r="DN3" s="4"/>
-      <c r="DO3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1684,28 +1641,28 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="O4" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="P4" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
-      <c r="T4" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1798,15 +1755,10 @@
       <c r="DH4" s="4"/>
       <c r="DI4" s="4"/>
       <c r="DJ4" s="4"/>
-      <c r="DK4" s="4"/>
-      <c r="DL4" s="4"/>
-      <c r="DM4" s="4"/>
-      <c r="DN4" s="4"/>
-      <c r="DO4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1817,28 +1769,28 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="K5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="O5" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="P5" s="4" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>143</v>
-      </c>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
@@ -1931,13 +1883,8 @@
       <c r="DH5" s="4"/>
       <c r="DI5" s="4"/>
       <c r="DJ5" s="4"/>
-      <c r="DK5" s="4"/>
-      <c r="DL5" s="4"/>
-      <c r="DM5" s="4"/>
-      <c r="DN5" s="4"/>
-      <c r="DO5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2052,62 +1999,57 @@
       <c r="DH6" s="3"/>
       <c r="DI6" s="3"/>
       <c r="DJ6" s="3"/>
-      <c r="DK6" s="3"/>
-      <c r="DL6" s="3"/>
-      <c r="DM6" s="3"/>
-      <c r="DN6" s="3"/>
-      <c r="DO6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="O7" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="Q7" s="3"/>
-      <c r="R7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
@@ -2201,15 +2143,10 @@
       <c r="DH7" s="3"/>
       <c r="DI7" s="3"/>
       <c r="DJ7" s="3"/>
-      <c r="DK7" s="3"/>
-      <c r="DL7" s="3"/>
-      <c r="DM7" s="3"/>
-      <c r="DN7" s="3"/>
-      <c r="DO7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2220,25 +2157,25 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="K8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+      <c r="O8" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="P8" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>154</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>143</v>
-      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
@@ -2332,15 +2269,10 @@
       <c r="DH8" s="4"/>
       <c r="DI8" s="4"/>
       <c r="DJ8" s="4"/>
-      <c r="DK8" s="4"/>
-      <c r="DL8" s="4"/>
-      <c r="DM8" s="4"/>
-      <c r="DN8" s="4"/>
-      <c r="DO8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2351,25 +2283,25 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+      <c r="K9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
+      <c r="O9" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="P9" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>156</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
-      <c r="T9" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>158</v>
-      </c>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
@@ -2463,15 +2395,10 @@
       <c r="DH9" s="4"/>
       <c r="DI9" s="4"/>
       <c r="DJ9" s="4"/>
-      <c r="DK9" s="4"/>
-      <c r="DL9" s="4"/>
-      <c r="DM9" s="4"/>
-      <c r="DN9" s="4"/>
-      <c r="DO9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2482,25 +2409,25 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="K10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="O10" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="P10" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>159</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
-      <c r="T10" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>161</v>
-      </c>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
@@ -2594,11 +2521,6 @@
       <c r="DH10" s="4"/>
       <c r="DI10" s="4"/>
       <c r="DJ10" s="4"/>
-      <c r="DK10" s="4"/>
-      <c r="DL10" s="4"/>
-      <c r="DM10" s="4"/>
-      <c r="DN10" s="4"/>
-      <c r="DO10" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2638,7 +2560,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2646,82 +2568,82 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2729,37 +2651,37 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2767,27 +2689,27 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2795,27 +2717,27 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2823,7 +2745,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2831,17 +2753,17 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2849,17 +2771,17 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2867,17 +2789,17 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,17 +2807,17 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2903,17 +2825,17 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2921,17 +2843,17 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2939,17 +2861,17 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2957,12 +2879,12 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2970,67 +2892,67 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
